--- a/data/trans_orig/IEDAD_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IEDAD_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33287</t>
+          <t>33370</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51404</t>
+          <t>51468</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41310</t>
+          <t>40273</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>59683</t>
+          <t>59169</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>26,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78431</t>
+          <t>79368</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102785</t>
+          <t>105245</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>36,07%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15469</t>
+          <t>15444</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29763</t>
+          <t>30009</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24201</t>
+          <t>23911</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40446</t>
+          <t>40226</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43337</t>
+          <t>43952</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>65178</t>
+          <t>65847</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,57%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44095</t>
+          <t>44731</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>63542</t>
+          <t>62557</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36096</t>
+          <t>37477</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54544</t>
+          <t>55189</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>36,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>86505</t>
+          <t>85117</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112810</t>
+          <t>112615</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,59%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>15085</t>
+          <t>14725</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28121</t>
+          <t>28587</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19937</t>
+          <t>19767</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35899</t>
+          <t>35373</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>38676</t>
+          <t>37614</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59195</t>
+          <t>58414</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,02%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52922</t>
+          <t>53005</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>73275</t>
+          <t>73888</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51505</t>
+          <t>50207</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71505</t>
+          <t>71166</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>107824</t>
+          <t>108072</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>136303</t>
+          <t>138417</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,98%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>34438</t>
+          <t>33905</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52421</t>
+          <t>51822</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>32064</t>
+          <t>31266</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50301</t>
+          <t>49728</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>70689</t>
+          <t>69227</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>95724</t>
+          <t>95511</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>52639</t>
+          <t>52423</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72435</t>
+          <t>72715</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66329</t>
+          <t>67930</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89177</t>
+          <t>90358</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,04%</t>
+          <t>42,59%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125862</t>
+          <t>125238</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>155792</t>
+          <t>156233</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20283</t>
+          <t>20899</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>35759</t>
+          <t>36216</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25033</t>
+          <t>25910</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42664</t>
+          <t>42715</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>50449</t>
+          <t>50657</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>73846</t>
+          <t>72819</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>17,88%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32846</t>
+          <t>32910</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50616</t>
+          <t>49646</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>32736</t>
+          <t>33267</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50202</t>
+          <t>50976</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>71072</t>
+          <t>69969</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>94688</t>
+          <t>93894</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,66%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14067</t>
+          <t>14388</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>27103</t>
+          <t>26768</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>18777</t>
+          <t>19520</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33706</t>
+          <t>33662</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>36306</t>
+          <t>37006</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>55909</t>
+          <t>56270</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,57%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46095</t>
+          <t>46025</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63589</t>
+          <t>62371</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>47305</t>
+          <t>47915</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>66709</t>
+          <t>66752</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,61%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>98163</t>
+          <t>98973</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124413</t>
+          <t>124019</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,14%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16455</t>
+          <t>16643</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29378</t>
+          <t>29575</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18762</t>
+          <t>19169</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33606</t>
+          <t>33657</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39369</t>
+          <t>39157</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57758</t>
+          <t>58854</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,47%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39065</t>
+          <t>39579</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58741</t>
+          <t>60142</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45107</t>
+          <t>46495</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66044</t>
+          <t>67816</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,63%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>90893</t>
+          <t>90990</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>119233</t>
+          <t>119680</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>34128</t>
+          <t>34428</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>54403</t>
+          <t>54583</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34347</t>
+          <t>34775</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>53499</t>
+          <t>53617</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>73738</t>
+          <t>73151</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>102659</t>
+          <t>100568</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>69514</t>
+          <t>70311</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>93899</t>
+          <t>93440</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,86%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>61267</t>
+          <t>62867</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>84528</t>
+          <t>83851</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>137865</t>
+          <t>140062</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>170789</t>
+          <t>171779</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,18%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26559</t>
+          <t>26368</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>45375</t>
+          <t>45633</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28609</t>
+          <t>27718</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45328</t>
+          <t>45865</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>57627</t>
+          <t>59306</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>82658</t>
+          <t>84827</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>176918</t>
+          <t>174392</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>215483</t>
+          <t>212913</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>185448</t>
+          <t>188174</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>224798</t>
+          <t>226172</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>374384</t>
+          <t>373291</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>427281</t>
+          <t>427089</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>112564</t>
+          <t>112728</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>143706</t>
+          <t>145480</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>125776</t>
+          <t>125746</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>159022</t>
+          <t>159656</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>246479</t>
+          <t>245732</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>292833</t>
+          <t>297555</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>231873</t>
+          <t>233216</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>272968</t>
+          <t>272686</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>232594</t>
+          <t>234349</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>273450</t>
+          <t>275249</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>478858</t>
+          <t>480680</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>538407</t>
+          <t>536203</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>91204</t>
+          <t>91643</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>121881</t>
+          <t>121584</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>107083</t>
+          <t>106414</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>140216</t>
+          <t>137806</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>205937</t>
+          <t>205330</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>250011</t>
+          <t>250017</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23373</t>
+          <t>24195</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41171</t>
+          <t>41790</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37808</t>
+          <t>37458</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>56763</t>
+          <t>56494</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66381</t>
+          <t>66065</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91288</t>
+          <t>90981</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,58%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26261</t>
+          <t>25630</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42718</t>
+          <t>42332</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19211</t>
+          <t>18237</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34983</t>
+          <t>35478</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49408</t>
+          <t>49385</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>74067</t>
+          <t>71785</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,19%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>41814</t>
+          <t>41076</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>61939</t>
+          <t>61068</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58773</t>
+          <t>59147</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>38,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>85992</t>
+          <t>85131</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>114139</t>
+          <t>113350</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,82%</t>
+          <t>38,55%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>16085</t>
+          <t>15762</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>29917</t>
+          <t>30715</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25307</t>
+          <t>24914</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42174</t>
+          <t>41439</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>45334</t>
+          <t>45457</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>67955</t>
+          <t>67220</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38075</t>
+          <t>38486</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57352</t>
+          <t>58054</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43570</t>
+          <t>43735</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63520</t>
+          <t>63249</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>89067</t>
+          <t>87313</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>117537</t>
+          <t>115757</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>26,91%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42035</t>
+          <t>41731</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62103</t>
+          <t>61251</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37493</t>
+          <t>37033</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57350</t>
+          <t>56527</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>84695</t>
+          <t>85144</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112197</t>
+          <t>111258</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>55990</t>
+          <t>55035</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>76650</t>
+          <t>77434</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>70340</t>
+          <t>71828</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>94076</t>
+          <t>94908</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,03%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133358</t>
+          <t>133535</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164638</t>
+          <t>164288</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>31,04%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,19%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31745</t>
+          <t>32909</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>49699</t>
+          <t>51419</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>33427</t>
+          <t>31845</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>51863</t>
+          <t>51439</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>70408</t>
+          <t>69614</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>96964</t>
+          <t>95649</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28710</t>
+          <t>27830</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>45535</t>
+          <t>44786</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24108</t>
+          <t>25214</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40363</t>
+          <t>40371</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,7 +4998,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57051</t>
+          <t>57304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>81347</t>
+          <t>80720</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,07%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>24421</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>39567</t>
+          <t>40914</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30287</t>
+          <t>30393</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>48480</t>
+          <t>47343</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>58491</t>
+          <t>59393</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>84297</t>
+          <t>83133</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43129</t>
+          <t>44060</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61898</t>
+          <t>62239</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,06%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>53383</t>
+          <t>55261</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74286</t>
+          <t>74697</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101727</t>
+          <t>102760</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>130766</t>
+          <t>130718</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>40,6%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27164</t>
+          <t>26243</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43920</t>
+          <t>43513</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24729</t>
+          <t>24728</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40719</t>
+          <t>41328</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5342,7 +5342,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>56264</t>
+          <t>56446</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>79227</t>
+          <t>80167</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45560</t>
+          <t>45223</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67044</t>
+          <t>66371</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39215</t>
+          <t>38511</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59054</t>
+          <t>59416</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>89230</t>
+          <t>88132</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>118264</t>
+          <t>118938</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>28,41%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>31051</t>
+          <t>31093</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>51045</t>
+          <t>50365</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>37292</t>
+          <t>37777</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>57896</t>
+          <t>58386</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>73796</t>
+          <t>72828</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>103633</t>
+          <t>102575</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>54471</t>
+          <t>55860</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>77897</t>
+          <t>79503</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>62287</t>
+          <t>61835</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>85379</t>
+          <t>84268</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>123449</t>
+          <t>124425</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>155850</t>
+          <t>157384</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38256</t>
+          <t>38483</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60103</t>
+          <t>58815</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,58%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30076</t>
+          <t>31126</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49674</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>73804</t>
+          <t>73924</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>102164</t>
+          <t>102077</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,38%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>152255</t>
+          <t>154366</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>190566</t>
+          <t>190414</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>162362</t>
+          <t>161335</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>201066</t>
+          <t>198535</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>321865</t>
+          <t>326199</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>376770</t>
+          <t>377890</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>137787</t>
+          <t>138923</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>175993</t>
+          <t>174947</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>140871</t>
+          <t>139228</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>174887</t>
+          <t>177014</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>290145</t>
+          <t>288333</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>341985</t>
+          <t>342035</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>215350</t>
+          <t>215093</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>255666</t>
+          <t>257090</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>247939</t>
+          <t>247597</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>293324</t>
+          <t>289938</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>475002</t>
+          <t>475753</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>534777</t>
+          <t>534210</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>129366</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>165299</t>
+          <t>166261</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>128835</t>
+          <t>128342</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>163947</t>
+          <t>164038</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>268411</t>
+          <t>269972</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>316852</t>
+          <t>320615</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28039</t>
+          <t>28880</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45926</t>
+          <t>46291</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23900</t>
+          <t>23699</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41024</t>
+          <t>40877</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56866</t>
+          <t>55819</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81252</t>
+          <t>81712</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,0%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27813</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44822</t>
+          <t>45371</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33026</t>
+          <t>32715</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51639</t>
+          <t>51577</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>65729</t>
+          <t>64815</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>92344</t>
+          <t>91341</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,42%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28829</t>
+          <t>28613</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45452</t>
+          <t>45696</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,99%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>35312</t>
+          <t>35043</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54757</t>
+          <t>53570</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,98%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>67914</t>
+          <t>67086</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>94387</t>
+          <t>92842</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>32,95%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18000</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32955</t>
+          <t>33202</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22705</t>
+          <t>22157</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39358</t>
+          <t>38000</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>44284</t>
+          <t>44673</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66301</t>
+          <t>67774</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45493</t>
+          <t>45684</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66211</t>
+          <t>65260</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41392</t>
+          <t>41137</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62040</t>
+          <t>61932</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>91912</t>
+          <t>92517</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>122640</t>
+          <t>121772</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,21%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42979</t>
+          <t>44106</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63207</t>
+          <t>64140</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>47186</t>
+          <t>46681</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68722</t>
+          <t>66960</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96330</t>
+          <t>95255</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>124529</t>
+          <t>123630</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,64%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>49461</t>
+          <t>50844</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70781</t>
+          <t>70166</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66608</t>
+          <t>66171</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>89583</t>
+          <t>87480</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>121495</t>
+          <t>121910</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>151400</t>
+          <t>152683</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,38%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>31603</t>
+          <t>31867</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48063</t>
+          <t>48508</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31325</t>
+          <t>30884</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>49831</t>
+          <t>50235</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>65976</t>
+          <t>65685</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>91617</t>
+          <t>91364</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30045</t>
+          <t>30200</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47048</t>
+          <t>47355</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27142</t>
+          <t>28348</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>45969</t>
+          <t>46843</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>27,58%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>62255</t>
+          <t>62034</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>86971</t>
+          <t>87632</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>27,16%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26361</t>
+          <t>26522</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>42596</t>
+          <t>42475</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33202</t>
+          <t>32386</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>51181</t>
+          <t>51447</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19,92%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>63957</t>
+          <t>63200</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>87933</t>
+          <t>88942</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,56%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>50092</t>
+          <t>49824</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68250</t>
+          <t>67701</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54134</t>
+          <t>54782</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74278</t>
+          <t>75538</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>45,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108350</t>
+          <t>108755</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136988</t>
+          <t>137523</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,62%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19609</t>
+          <t>19520</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32666</t>
+          <t>33758</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17565</t>
+          <t>17491</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32301</t>
+          <t>31622</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39873</t>
+          <t>40014</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59729</t>
+          <t>59414</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>31961</t>
+          <t>32463</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>53123</t>
+          <t>53252</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>45291</t>
+          <t>46419</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66033</t>
+          <t>66914</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>83033</t>
+          <t>83237</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111889</t>
+          <t>113587</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>27,49%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>55150</t>
+          <t>55802</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>78026</t>
+          <t>79273</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,62%</t>
+          <t>38,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39154</t>
+          <t>38865</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>59406</t>
+          <t>58673</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>98260</t>
+          <t>97749</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>130385</t>
+          <t>130746</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,78%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,65%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>45085</t>
+          <t>44869</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>66396</t>
+          <t>66607</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>60682</t>
+          <t>61716</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>82766</t>
+          <t>82708</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>111565</t>
+          <t>113571</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>143530</t>
+          <t>144082</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33429</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52858</t>
+          <t>52851</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,7 +8948,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,39%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>23127</t>
+          <t>22573</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39617</t>
+          <t>39064</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>60842</t>
+          <t>61223</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>86421</t>
+          <t>86354</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,9%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>155049</t>
+          <t>156443</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>192500</t>
+          <t>193240</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>156425</t>
+          <t>154538</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>193690</t>
+          <t>194595</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>322658</t>
+          <t>320810</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>375614</t>
+          <t>377871</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>171593</t>
+          <t>169578</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>210006</t>
+          <t>209164</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>169707</t>
+          <t>168486</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>210307</t>
+          <t>209482</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>350807</t>
+          <t>350141</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>404421</t>
+          <t>407339</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>192733</t>
+          <t>191420</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>231983</t>
+          <t>230469</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>238355</t>
+          <t>236554</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>279662</t>
+          <t>280704</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>438565</t>
+          <t>438129</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>497185</t>
+          <t>495088</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>115609</t>
+          <t>116930</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>149111</t>
+          <t>149315</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>108097</t>
+          <t>108183</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>142287</t>
+          <t>140319</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>233349</t>
+          <t>232145</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>278610</t>
+          <t>280910</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36776</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54542</t>
+          <t>54660</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>46,51%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44854</t>
+          <t>46451</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79023</t>
+          <t>79932</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>87572</t>
+          <t>88918</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>125541</t>
+          <t>127932</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>49,65%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20233</t>
+          <t>20290</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34780</t>
+          <t>35192</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28488</t>
+          <t>28654</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>52346</t>
+          <t>52196</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,29%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>53224</t>
+          <t>53206</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81212</t>
+          <t>80576</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10167,7 +10167,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28647</t>
+          <t>27917</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>44003</t>
+          <t>43335</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>21723</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>41514</t>
+          <t>42047</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>53590</t>
+          <t>54604</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80180</t>
+          <t>79592</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,89%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6499</t>
+          <t>6311</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14362</t>
+          <t>14137</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5670</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15796</t>
+          <t>15907</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13788</t>
+          <t>13916</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26924</t>
+          <t>26424</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>10,25%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64622</t>
+          <t>66777</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90988</t>
+          <t>93232</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>83256</t>
+          <t>82872</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>113966</t>
+          <t>113186</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,49%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>155710</t>
+          <t>156893</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>196471</t>
+          <t>197370</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>44,3%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>42561</t>
+          <t>42399</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>64378</t>
+          <t>63596</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64914</t>
+          <t>66130</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>91894</t>
+          <t>92038</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114504</t>
+          <t>115259</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149499</t>
+          <t>150677</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,82%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35894</t>
+          <t>34993</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55118</t>
+          <t>54868</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>42443</t>
+          <t>43242</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>65895</t>
+          <t>64676</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>84714</t>
+          <t>84473</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>115055</t>
+          <t>114085</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>9904</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21343</t>
+          <t>21837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18689</t>
+          <t>18863</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33843</t>
+          <t>33507</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>31844</t>
+          <t>31168</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>50903</t>
+          <t>48891</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>10,97%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>68195</t>
+          <t>66282</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131915</t>
+          <t>129475</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>67064</t>
+          <t>68094</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>96058</t>
+          <t>95946</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146224</t>
+          <t>143370</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>216909</t>
+          <t>219905</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>58,53%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26355</t>
+          <t>28575</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>60537</t>
+          <t>61517</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>36283</t>
+          <t>37016</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61833</t>
+          <t>62522</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>69699</t>
+          <t>70597</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>112776</t>
+          <t>113837</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,3%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27214</t>
+          <t>25023</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57757</t>
+          <t>57094</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,33%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36392</t>
+          <t>35425</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>58030</t>
+          <t>57314</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>68146</t>
+          <t>67634</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>106763</t>
+          <t>107948</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,73%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6544</t>
+          <t>6675</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19479</t>
+          <t>18533</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6338</t>
+          <t>6246</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16300</t>
+          <t>16342</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15176</t>
+          <t>16025</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30551</t>
+          <t>31866</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,48%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>53995</t>
+          <t>53811</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>74678</t>
+          <t>74906</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>44,46%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55980</t>
+          <t>56658</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79319</t>
+          <t>79548</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>30,89%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115604</t>
+          <t>116055</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>147586</t>
+          <t>145247</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>41,59%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>39515</t>
+          <t>38329</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>59093</t>
+          <t>58153</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35962</t>
+          <t>36276</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>58667</t>
+          <t>57758</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>81005</t>
+          <t>81575</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>110307</t>
+          <t>110628</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,68%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27588</t>
+          <t>27257</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>46124</t>
+          <t>45343</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>41804</t>
+          <t>40979</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64286</t>
+          <t>61881</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,47%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>73044</t>
+          <t>73173</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>100545</t>
+          <t>100050</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>28,65%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14916</t>
+          <t>15267</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>29313</t>
+          <t>28936</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9933</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22957</t>
+          <t>21997</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>27895</t>
+          <t>28423</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>46549</t>
+          <t>47443</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,59%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>248472</t>
+          <t>247240</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>322651</t>
+          <t>323452</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>277715</t>
+          <t>276995</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>338660</t>
+          <t>336727</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>539835</t>
+          <t>543523</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>639610</t>
+          <t>643524</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>45,06%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>151147</t>
+          <t>145139</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>198210</t>
+          <t>195225</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>188530</t>
+          <t>187258</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>238720</t>
+          <t>237344</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>347942</t>
+          <t>348662</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>421344</t>
+          <t>419329</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>136171</t>
+          <t>137267</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>179549</t>
+          <t>179493</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>162289</t>
+          <t>161554</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>204711</t>
+          <t>206013</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>311536</t>
+          <t>311091</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>371951</t>
+          <t>372772</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>46656</t>
+          <t>45672</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>71062</t>
+          <t>68830</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>49785</t>
+          <t>50215</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>74241</t>
+          <t>74921</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>103482</t>
+          <t>102424</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>137351</t>
+          <t>134589</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
